--- a/aca/Grundlagen/2026-30-04_S4_Kürzungshilfe Vertragsbeschreibung.xlsx
+++ b/aca/Grundlagen/2026-30-04_S4_Kürzungshilfe Vertragsbeschreibung.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sbb.sharepoint.com/sites/vertragsmanagement/Freigegebene Dokumente/General/10 Superuser/00 - Projekt Datenqualität &amp; Migration S4/07 H4R/Grundlagen/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sbb-my.sharepoint.com/personal/samuel_engel_sbb_ch/Documents/Documents/GitHub/A38/aca/Grundlagen/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="8_{1D104731-1B2E-40A5-88F7-3115A6785226}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F6416F0-A345-4050-A858-BFF1EF7A2618}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5163AB33-29A8-4429-99A0-BCBB55480B3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{FA6439BA-096A-4E1A-B2B3-AC0DF5587D0A}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{FA6439BA-096A-4E1A-B2B3-AC0DF5587D0A}"/>
   </bookViews>
   <sheets>
     <sheet name="Kürzungshilfe" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="103">
   <si>
     <t>S4 Feld Vertragsbeschreibung / S4 Champ Description du contrat</t>
   </si>
@@ -72,6 +72,9 @@
     <t>→</t>
   </si>
   <si>
+    <t>FinVer PZM Margarethen Zusatzmod. (AS35)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Anzahl Zeichen  / Nombre de caractères </t>
   </si>
   <si>
@@ -234,72 +237,75 @@
     <t>Convention</t>
   </si>
   <si>
+    <t>Conv. / cvt</t>
+  </si>
+  <si>
+    <t>Ognuno può completare l’elenco con abbreviazioni di uso comune e note!</t>
+  </si>
+  <si>
+    <t>Italienisch</t>
+  </si>
+  <si>
+    <t>Stazione</t>
+  </si>
+  <si>
+    <t>Staz.</t>
+  </si>
+  <si>
+    <t>Mantenimento dei manufatti</t>
+  </si>
+  <si>
+    <t>Mant. manuf.</t>
+  </si>
+  <si>
+    <t>Contratto</t>
+  </si>
+  <si>
+    <t>Contr.</t>
+  </si>
+  <si>
+    <t>Esercizio</t>
+  </si>
+  <si>
+    <t>Eserc.</t>
+  </si>
+  <si>
+    <t>Rinnovo</t>
+  </si>
+  <si>
+    <t>Rinn.</t>
+  </si>
+  <si>
+    <t>Comune</t>
+  </si>
+  <si>
+    <t>Cantone</t>
+  </si>
+  <si>
+    <t>Sovrappasso</t>
+  </si>
+  <si>
+    <t>SVP</t>
+  </si>
+  <si>
+    <t>Sottopasso</t>
+  </si>
+  <si>
+    <t>STP</t>
+  </si>
+  <si>
+    <t>Manutenzione</t>
+  </si>
+  <si>
+    <t>Manut.</t>
+  </si>
+  <si>
+    <t>Convenzione</t>
+  </si>
+  <si>
     <t>Conv.</t>
   </si>
   <si>
-    <t>Ognuno può completare l’elenco con abbreviazioni di uso comune e note!</t>
-  </si>
-  <si>
-    <t>Italienisch</t>
-  </si>
-  <si>
-    <t>Stazione</t>
-  </si>
-  <si>
-    <t>Staz.</t>
-  </si>
-  <si>
-    <t>Mantenimento dei manufatti</t>
-  </si>
-  <si>
-    <t>Mant. manuf.</t>
-  </si>
-  <si>
-    <t>Contratto</t>
-  </si>
-  <si>
-    <t>Contr.</t>
-  </si>
-  <si>
-    <t>Esercizio</t>
-  </si>
-  <si>
-    <t>Eserc.</t>
-  </si>
-  <si>
-    <t>Rinnovo</t>
-  </si>
-  <si>
-    <t>Rinn.</t>
-  </si>
-  <si>
-    <t>Comune</t>
-  </si>
-  <si>
-    <t>Cantone</t>
-  </si>
-  <si>
-    <t>Sovrappasso</t>
-  </si>
-  <si>
-    <t>SVP</t>
-  </si>
-  <si>
-    <t>Sottopasso</t>
-  </si>
-  <si>
-    <t>STP</t>
-  </si>
-  <si>
-    <t>Manutenzione</t>
-  </si>
-  <si>
-    <t>Manut.</t>
-  </si>
-  <si>
-    <t>Convenzione</t>
-  </si>
-  <si>
     <t>S4 Feld Vertragsbeschreibung</t>
   </si>
   <si>
@@ -360,7 +366,10 @@
     <t>Unterhalts-, Erneuerungs- und Änderungskosten von Kreuzungsbauwerken Bahngleise - Kantonsstrassen / künstliche Gewässer</t>
   </si>
   <si>
-    <t>Anker Wanne West Tunnel Hausmatt</t>
+    <t>Finanzierungsvereinbarung</t>
+  </si>
+  <si>
+    <t>FinVer</t>
   </si>
 </sst>
 </file>
@@ -546,7 +555,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Standard 2" xfId="1" xr:uid="{1A3EBDAA-BE4D-4CD2-80B3-CE6D28C039B5}"/>
   </cellStyles>
   <dxfs count="1">
@@ -1012,15 +1021,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EB2CBFC-6A85-4F07-8171-8E0C9A5EB559}">
   <dimension ref="A1:CX6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3828125" defaultRowHeight="12.45" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="36.6640625" customWidth="1"/>
-    <col min="2" max="2" width="6.109375" customWidth="1"/>
-    <col min="3" max="101" width="2.88671875" customWidth="1"/>
+    <col min="1" max="1" width="36.69140625" customWidth="1"/>
+    <col min="2" max="2" width="6.15234375" customWidth="1"/>
+    <col min="3" max="101" width="2.84375" customWidth="1"/>
     <col min="102" max="102" width="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:102" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:102" ht="14.6" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1060,7 +1069,7 @@
       <c r="AI1" s="2"/>
       <c r="AJ1" s="2"/>
     </row>
-    <row r="3" spans="1:102" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:102" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
@@ -1068,7 +1077,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>99</v>
+        <v>3</v>
       </c>
       <c r="D3" s="19"/>
       <c r="E3" s="19"/>
@@ -1170,9 +1179,9 @@
       <c r="CW3" s="19"/>
       <c r="CX3" s="19"/>
     </row>
-    <row r="4" spans="1:102" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:102" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" s="3">
         <v>1</v>
@@ -1475,115 +1484,131 @@
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:102" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:102" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C5" s="5" t="str" cm="1">
-        <f t="array" ref="C5:AH5">MID(C3,_xlfn.SEQUENCE(1,LEN(C3)),1)</f>
+        <f t="array" ref="C5:AP5">MID(C3,_xlfn.SEQUENCE(1,LEN(C3)),1)</f>
+        <v>F</v>
+      </c>
+      <c r="D5" s="5" t="str">
+        <v>i</v>
+      </c>
+      <c r="E5" s="5" t="str">
+        <v>n</v>
+      </c>
+      <c r="F5" s="5" t="str">
+        <v>V</v>
+      </c>
+      <c r="G5" s="5" t="str">
+        <v>e</v>
+      </c>
+      <c r="H5" s="5" t="str">
+        <v>r</v>
+      </c>
+      <c r="I5" s="5" t="str">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J5" s="5" t="str">
+        <v>P</v>
+      </c>
+      <c r="K5" s="5" t="str">
+        <v>Z</v>
+      </c>
+      <c r="L5" s="5" t="str">
+        <v>M</v>
+      </c>
+      <c r="M5" s="5" t="str">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="N5" s="5" t="str">
+        <v>M</v>
+      </c>
+      <c r="O5" s="5" t="str">
+        <v>a</v>
+      </c>
+      <c r="P5" s="5" t="str">
+        <v>r</v>
+      </c>
+      <c r="Q5" s="5" t="str">
+        <v>g</v>
+      </c>
+      <c r="R5" s="5" t="str">
+        <v>a</v>
+      </c>
+      <c r="S5" s="5" t="str">
+        <v>r</v>
+      </c>
+      <c r="T5" s="5" t="str">
+        <v>e</v>
+      </c>
+      <c r="U5" s="5" t="str">
+        <v>t</v>
+      </c>
+      <c r="V5" s="5" t="str">
+        <v>h</v>
+      </c>
+      <c r="W5" s="5" t="str">
+        <v>e</v>
+      </c>
+      <c r="X5" s="5" t="str">
+        <v>n</v>
+      </c>
+      <c r="Y5" s="5" t="str">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="Z5" s="5" t="str">
+        <v>Z</v>
+      </c>
+      <c r="AA5" s="5" t="str">
+        <v>u</v>
+      </c>
+      <c r="AB5" s="5" t="str">
+        <v>s</v>
+      </c>
+      <c r="AC5" s="5" t="str">
+        <v>a</v>
+      </c>
+      <c r="AD5" s="5" t="str">
+        <v>t</v>
+      </c>
+      <c r="AE5" s="5" t="str">
+        <v>z</v>
+      </c>
+      <c r="AF5" s="5" t="str">
+        <v>m</v>
+      </c>
+      <c r="AG5" s="5" t="str">
+        <v>o</v>
+      </c>
+      <c r="AH5" s="5" t="str">
+        <v>d</v>
+      </c>
+      <c r="AI5" s="5" t="str">
+        <v>.</v>
+      </c>
+      <c r="AJ5" s="5" t="str">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="AK5" s="5" t="str">
+        <v>(</v>
+      </c>
+      <c r="AL5" s="5" t="str">
         <v>A</v>
       </c>
-      <c r="D5" s="5" t="str">
-        <v>n</v>
-      </c>
-      <c r="E5" s="5" t="str">
-        <v>k</v>
-      </c>
-      <c r="F5" s="5" t="str">
-        <v>e</v>
-      </c>
-      <c r="G5" s="5" t="str">
-        <v>r</v>
-      </c>
-      <c r="H5" s="5" t="str">
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="I5" s="5" t="str">
-        <v>W</v>
-      </c>
-      <c r="J5" s="5" t="str">
-        <v>a</v>
-      </c>
-      <c r="K5" s="5" t="str">
-        <v>n</v>
-      </c>
-      <c r="L5" s="5" t="str">
-        <v>n</v>
-      </c>
-      <c r="M5" s="5" t="str">
-        <v>e</v>
-      </c>
-      <c r="N5" s="5" t="str">
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="O5" s="5" t="str">
-        <v>W</v>
-      </c>
-      <c r="P5" s="5" t="str">
-        <v>e</v>
-      </c>
-      <c r="Q5" s="5" t="str">
-        <v>s</v>
-      </c>
-      <c r="R5" s="5" t="str">
-        <v>t</v>
-      </c>
-      <c r="S5" s="5" t="str">
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="T5" s="5" t="str">
-        <v>T</v>
-      </c>
-      <c r="U5" s="5" t="str">
-        <v>u</v>
-      </c>
-      <c r="V5" s="5" t="str">
-        <v>n</v>
-      </c>
-      <c r="W5" s="5" t="str">
-        <v>n</v>
-      </c>
-      <c r="X5" s="5" t="str">
-        <v>e</v>
-      </c>
-      <c r="Y5" s="5" t="str">
-        <v>l</v>
-      </c>
-      <c r="Z5" s="5" t="str">
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="AA5" s="5" t="str">
-        <v>H</v>
-      </c>
-      <c r="AB5" s="5" t="str">
-        <v>a</v>
-      </c>
-      <c r="AC5" s="5" t="str">
-        <v>u</v>
-      </c>
-      <c r="AD5" s="5" t="str">
-        <v>s</v>
-      </c>
-      <c r="AE5" s="5" t="str">
-        <v>m</v>
-      </c>
-      <c r="AF5" s="5" t="str">
-        <v>a</v>
-      </c>
-      <c r="AG5" s="5" t="str">
-        <v>t</v>
-      </c>
-      <c r="AH5" s="5" t="str">
-        <v>t</v>
-      </c>
-      <c r="AI5" s="5"/>
-      <c r="AJ5" s="5"/>
-      <c r="AK5" s="5"/>
-      <c r="AL5" s="5"/>
-      <c r="AM5" s="5"/>
-      <c r="AN5" s="5"/>
-      <c r="AO5" s="5"/>
-      <c r="AP5" s="5"/>
+      <c r="AM5" s="5" t="str">
+        <v>S</v>
+      </c>
+      <c r="AN5" s="5" t="str">
+        <v>3</v>
+      </c>
+      <c r="AO5" s="5" t="str">
+        <v>5</v>
+      </c>
+      <c r="AP5" s="5" t="str">
+        <v>)</v>
+      </c>
       <c r="AQ5" s="11"/>
       <c r="AR5" s="11"/>
       <c r="AS5" s="11"/>
@@ -1645,7 +1670,7 @@
       <c r="CW5" s="11"/>
       <c r="CX5" s="11"/>
     </row>
-    <row r="6" spans="1:102" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:102" x14ac:dyDescent="0.3">
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
@@ -1764,330 +1789,338 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9288DDDE-EB4E-4021-A5BA-57447EBCB9AF}">
-  <dimension ref="A1:B45"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B46"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3828125" defaultRowHeight="12.45" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="6" width="23.109375" customWidth="1"/>
+    <col min="1" max="6" width="23.15234375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>101</v>
+      </c>
+      <c r="B18" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="18"/>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" t="s">
-        <v>11</v>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" t="s">
+        <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" t="s">
-        <v>13</v>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>43</v>
+      </c>
+      <c r="B24" t="s">
+        <v>44</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" t="s">
-        <v>15</v>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" t="s">
+        <v>46</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" t="s">
-        <v>17</v>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>47</v>
+      </c>
+      <c r="B26" t="s">
+        <v>48</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" t="s">
-        <v>19</v>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>49</v>
+      </c>
+      <c r="B27" t="s">
+        <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" t="s">
-        <v>21</v>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>51</v>
+      </c>
+      <c r="B28" t="s">
+        <v>52</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10" t="s">
-        <v>23</v>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>53</v>
+      </c>
+      <c r="B29" t="s">
+        <v>54</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" t="s">
-        <v>25</v>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>55</v>
+      </c>
+      <c r="B30" t="s">
+        <v>56</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" t="s">
-        <v>27</v>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>57</v>
+      </c>
+      <c r="B31" t="s">
+        <v>58</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>28</v>
-      </c>
-      <c r="B13" t="s">
-        <v>29</v>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" s="18" t="s">
+        <v>59</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>30</v>
-      </c>
-      <c r="B14" t="s">
-        <v>31</v>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="B35" s="15" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>32</v>
-      </c>
-      <c r="B15" t="s">
-        <v>33</v>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>61</v>
+      </c>
+      <c r="B36" t="s">
+        <v>62</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>34</v>
-      </c>
-      <c r="B16" t="s">
-        <v>35</v>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>63</v>
+      </c>
+      <c r="B37" t="s">
+        <v>64</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>36</v>
-      </c>
-      <c r="B17" t="s">
-        <v>37</v>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>65</v>
+      </c>
+      <c r="B38" t="s">
+        <v>66</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" s="18"/>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>67</v>
+      </c>
+      <c r="B39" t="s">
+        <v>68</v>
+      </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="B21" s="14" t="s">
-        <v>7</v>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>69</v>
+      </c>
+      <c r="B40" t="s">
+        <v>70</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>40</v>
-      </c>
-      <c r="B22" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>42</v>
-      </c>
-      <c r="B23" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>44</v>
-      </c>
-      <c r="B24" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>46</v>
-      </c>
-      <c r="B25" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>48</v>
-      </c>
-      <c r="B26" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>50</v>
-      </c>
-      <c r="B27" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>52</v>
-      </c>
-      <c r="B28" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>54</v>
-      </c>
-      <c r="B29" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>56</v>
-      </c>
-      <c r="B30" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="18" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="B34" s="15" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>60</v>
-      </c>
-      <c r="B35" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>62</v>
-      </c>
-      <c r="B36" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>64</v>
-      </c>
-      <c r="B37" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>66</v>
-      </c>
-      <c r="B38" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>68</v>
-      </c>
-      <c r="B39" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>70</v>
-      </c>
-      <c r="B40" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>71</v>
       </c>
       <c r="B41" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>72</v>
       </c>
       <c r="B42" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
         <v>73</v>
       </c>
+      <c r="B43" t="s">
+        <v>74</v>
+      </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>74</v>
-      </c>
-      <c r="B43" t="s">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
         <v>75</v>
       </c>
+      <c r="B44" t="s">
+        <v>76</v>
+      </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>76</v>
-      </c>
-      <c r="B44" t="s">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
         <v>77</v>
       </c>
+      <c r="B45" t="s">
+        <v>78</v>
+      </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>78</v>
-      </c>
-      <c r="B45" t="s">
-        <v>57</v>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>79</v>
+      </c>
+      <c r="B46" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -2102,20 +2135,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D321A29-5FB2-4B38-A6A2-9ACBF82794E0}">
   <dimension ref="A1:DQ45"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3828125" defaultRowHeight="12.45" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="100" width="2.88671875" customWidth="1"/>
+    <col min="1" max="1" width="29.53515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="100" width="2.84375" customWidth="1"/>
     <col min="101" max="101" width="4" bestFit="1" customWidth="1"/>
-    <col min="102" max="121" width="2.88671875" customWidth="1"/>
+    <col min="102" max="121" width="2.84375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:121" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:121" ht="14.6" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C1" s="12"/>
       <c r="D1" s="12"/>
@@ -2147,17 +2180,17 @@
       <c r="AD1" s="12"/>
       <c r="AE1" s="12"/>
     </row>
-    <row r="3" spans="1:121" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:121" ht="17.600000000000001" x14ac:dyDescent="0.4">
       <c r="A3" s="6" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
-    <row r="4" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B4" s="3">
         <v>1</v>
@@ -2480,9 +2513,9 @@
       <c r="DP4" s="4"/>
       <c r="DQ4" s="4"/>
     </row>
-    <row r="5" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B5" s="5" t="str" cm="1">
         <f t="array" ref="B5:N5">MID(B3,_xlfn.SEQUENCE(1,LEN(B3)),1)</f>
@@ -2632,7 +2665,7 @@
       <c r="DP5" s="11"/>
       <c r="DQ5" s="11"/>
     </row>
-    <row r="6" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:121" x14ac:dyDescent="0.3">
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
@@ -2754,12 +2787,12 @@
       <c r="DP6" s="5"/>
       <c r="DQ6" s="5"/>
     </row>
-    <row r="7" spans="1:121" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:121" ht="17.600000000000001" x14ac:dyDescent="0.4">
       <c r="A7" s="6" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
@@ -2881,9 +2914,9 @@
       <c r="DP7" s="5"/>
       <c r="DQ7" s="5"/>
     </row>
-    <row r="8" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B8" s="3">
         <v>1</v>
@@ -3206,9 +3239,9 @@
       <c r="DP8" s="4"/>
       <c r="DQ8" s="4"/>
     </row>
-    <row r="9" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B9" s="5" t="str" cm="1">
         <f t="array" ref="B9:U9">MID(B7,_xlfn.SEQUENCE(1,LEN(B7)),1)</f>
@@ -3372,7 +3405,7 @@
       <c r="DP9" s="11"/>
       <c r="DQ9" s="11"/>
     </row>
-    <row r="10" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:121" x14ac:dyDescent="0.3">
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
@@ -3494,12 +3527,12 @@
       <c r="DP10" s="5"/>
       <c r="DQ10" s="5"/>
     </row>
-    <row r="11" spans="1:121" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:121" ht="17.600000000000001" x14ac:dyDescent="0.4">
       <c r="A11" s="6" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
@@ -3621,9 +3654,9 @@
       <c r="DP11" s="5"/>
       <c r="DQ11" s="5"/>
     </row>
-    <row r="12" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B12" s="3">
         <v>1</v>
@@ -3946,9 +3979,9 @@
       <c r="DP12" s="4"/>
       <c r="DQ12" s="4"/>
     </row>
-    <row r="13" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B13" s="5" t="str" cm="1">
         <f t="array" ref="B13:O13">MID(B11,_xlfn.SEQUENCE(1,LEN(B11)),1)</f>
@@ -4100,7 +4133,7 @@
       <c r="DP13" s="11"/>
       <c r="DQ13" s="11"/>
     </row>
-    <row r="14" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:121" x14ac:dyDescent="0.3">
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
@@ -4222,12 +4255,12 @@
       <c r="DP14" s="5"/>
       <c r="DQ14" s="5"/>
     </row>
-    <row r="15" spans="1:121" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:121" ht="17.600000000000001" x14ac:dyDescent="0.4">
       <c r="A15" s="6" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
@@ -4349,9 +4382,9 @@
       <c r="DP15" s="5"/>
       <c r="DQ15" s="5"/>
     </row>
-    <row r="16" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B16" s="3">
         <v>1</v>
@@ -4674,9 +4707,9 @@
       <c r="DP16" s="4"/>
       <c r="DQ16" s="4"/>
     </row>
-    <row r="17" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B17" s="5" t="str" cm="1">
         <f t="array" ref="B17:R17">MID(B15,_xlfn.SEQUENCE(1,LEN(B15)),1)</f>
@@ -4834,7 +4867,7 @@
       <c r="DP17" s="11"/>
       <c r="DQ17" s="11"/>
     </row>
-    <row r="18" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:121" x14ac:dyDescent="0.3">
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
@@ -4956,12 +4989,12 @@
       <c r="DP18" s="5"/>
       <c r="DQ18" s="5"/>
     </row>
-    <row r="19" spans="1:121" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:121" ht="17.600000000000001" x14ac:dyDescent="0.4">
       <c r="A19" s="6" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
@@ -5083,9 +5116,9 @@
       <c r="DP19" s="5"/>
       <c r="DQ19" s="5"/>
     </row>
-    <row r="20" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B20" s="3">
         <v>1</v>
@@ -5408,9 +5441,9 @@
       <c r="DP20" s="4"/>
       <c r="DQ20" s="4"/>
     </row>
-    <row r="21" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B21" s="5" t="str" cm="1">
         <f t="array" ref="B21:R21">MID(B19,_xlfn.SEQUENCE(1,LEN(B19)),1)</f>
@@ -5568,12 +5601,12 @@
       <c r="DP21" s="11"/>
       <c r="DQ21" s="11"/>
     </row>
-    <row r="23" spans="1:121" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:121" ht="17.600000000000001" x14ac:dyDescent="0.4">
       <c r="A23" s="7" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="5"/>
@@ -5695,9 +5728,9 @@
       <c r="DP23" s="5"/>
       <c r="DQ23" s="5"/>
     </row>
-    <row r="24" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B24" s="3">
         <v>1</v>
@@ -6020,9 +6053,9 @@
       <c r="DP24" s="4"/>
       <c r="DQ24" s="4"/>
     </row>
-    <row r="25" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B25" s="5" t="str" cm="1">
         <f t="array" ref="B25:X25">MID(B23,_xlfn.SEQUENCE(1,LEN(B23)),1)</f>
@@ -6192,12 +6225,12 @@
       <c r="DP25" s="11"/>
       <c r="DQ25" s="11"/>
     </row>
-    <row r="27" spans="1:121" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:121" ht="17.600000000000001" x14ac:dyDescent="0.4">
       <c r="A27" s="7" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C27" s="5"/>
       <c r="D27" s="5"/>
@@ -6319,9 +6352,9 @@
       <c r="DP27" s="5"/>
       <c r="DQ27" s="5"/>
     </row>
-    <row r="28" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B28" s="3">
         <v>1</v>
@@ -6644,9 +6677,9 @@
       <c r="DP28" s="4"/>
       <c r="DQ28" s="4"/>
     </row>
-    <row r="29" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B29" s="5" t="str" cm="1">
         <f t="array" ref="B29:V29">MID(B27,_xlfn.SEQUENCE(1,LEN(B27)),1)</f>
@@ -6812,12 +6845,12 @@
       <c r="DP29" s="11"/>
       <c r="DQ29" s="11"/>
     </row>
-    <row r="31" spans="1:121" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:121" ht="17.600000000000001" x14ac:dyDescent="0.4">
       <c r="A31" s="8" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
@@ -6939,9 +6972,9 @@
       <c r="DP31" s="5"/>
       <c r="DQ31" s="5"/>
     </row>
-    <row r="32" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B32" s="3">
         <v>1</v>
@@ -7264,9 +7297,9 @@
       <c r="DP32" s="4"/>
       <c r="DQ32" s="4"/>
     </row>
-    <row r="33" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B33" s="5" t="str" cm="1">
         <f t="array" ref="B33:AH33">MID(B31,_xlfn.SEQUENCE(1,LEN(B31)),1)</f>
@@ -7456,12 +7489,12 @@
       <c r="DP33" s="11"/>
       <c r="DQ33" s="11"/>
     </row>
-    <row r="35" spans="1:121" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:121" ht="17.600000000000001" x14ac:dyDescent="0.4">
       <c r="A35" s="8" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C35" s="5"/>
       <c r="D35" s="5"/>
@@ -7583,9 +7616,9 @@
       <c r="DP35" s="5"/>
       <c r="DQ35" s="5"/>
     </row>
-    <row r="36" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B36" s="3">
         <v>1</v>
@@ -7908,9 +7941,9 @@
       <c r="DP36" s="4"/>
       <c r="DQ36" s="4"/>
     </row>
-    <row r="37" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B37" s="5" t="str" cm="1">
         <f t="array" ref="B37:BV37">MID(B35,_xlfn.SEQUENCE(1,LEN(B35)),1)</f>
@@ -8180,12 +8213,12 @@
       <c r="DP37" s="11"/>
       <c r="DQ37" s="11"/>
     </row>
-    <row r="39" spans="1:121" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:121" ht="17.600000000000001" x14ac:dyDescent="0.4">
       <c r="A39" s="9" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C39" s="5"/>
       <c r="D39" s="5"/>
@@ -8307,9 +8340,9 @@
       <c r="DP39" s="5"/>
       <c r="DQ39" s="5"/>
     </row>
-    <row r="40" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B40" s="3">
         <v>1</v>
@@ -8632,9 +8665,9 @@
       <c r="DP40" s="4"/>
       <c r="DQ40" s="4"/>
     </row>
-    <row r="41" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B41" s="5" t="str" cm="1">
         <f t="array" ref="B41:BL41">MID(B39,_xlfn.SEQUENCE(1,LEN(B39)),1)</f>
@@ -8884,12 +8917,12 @@
       <c r="DP41" s="11"/>
       <c r="DQ41" s="11"/>
     </row>
-    <row r="43" spans="1:121" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:121" ht="17.600000000000001" x14ac:dyDescent="0.4">
       <c r="A43" s="10" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C43" s="5"/>
       <c r="D43" s="5"/>
@@ -9011,9 +9044,9 @@
       <c r="DP43" s="5"/>
       <c r="DQ43" s="5"/>
     </row>
-    <row r="44" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B44" s="3">
         <v>1</v>
@@ -9336,9 +9369,9 @@
       <c r="DP44" s="4"/>
       <c r="DQ44" s="4"/>
     </row>
-    <row r="45" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B45" s="5" t="str" cm="1">
         <f t="array" ref="B45:DP45">MID(B43,_xlfn.SEQUENCE(1,LEN(B43)),1)</f>
@@ -9707,15 +9740,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="92de02f7-8a66-43c9-a10c-663538af82ca" xsi:nil="true"/>
@@ -9726,9 +9750,9 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x0101001C7FA2D65802E143AE544A8A0D4C7B9D" ma:contentTypeVersion="18" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="66721a2c7a24dbe07d80cd78972e9a3b">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9211a0c2-e439-43f6-b3c8-c1278e26f744" xmlns:ns3="92de02f7-8a66-43c9-a10c-663538af82ca" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="edc002b9fb8c6368e6700ccf595ed4fc" ns2:_="" ns3:_="">
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101001C7FA2D65802E143AE544A8A0D4C7B9D" ma:contentTypeVersion="18" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="0576b60033f3b3056fa5c1b37276830e">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9211a0c2-e439-43f6-b3c8-c1278e26f744" xmlns:ns3="92de02f7-8a66-43c9-a10c-663538af82ca" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="aa468cfe087c19721fa4110963e26f1b" ns2:_="" ns3:_="">
     <xsd:import namespace="9211a0c2-e439-43f6-b3c8-c1278e26f744"/>
     <xsd:import namespace="92de02f7-8a66-43c9-a10c-663538af82ca"/>
     <xsd:element name="properties">
@@ -9791,7 +9815,7 @@
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="14" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Bildmarkierungen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2e7e7b05-955d-4ec1-8c45-691041b8b004" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="14" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Balises d’images" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2e7e7b05-955d-4ec1-8c45-691041b8b004" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
@@ -9855,7 +9879,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithUsers" ma:index="20" nillable="true" ma:displayName="Freigegeben für" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="20" nillable="true" ma:displayName="Partagé avec" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -9874,7 +9898,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="21" nillable="true" ma:displayName="Freigegeben für - Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="21" nillable="true" ma:displayName="Partagé avec détails" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
@@ -9891,8 +9915,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Inhaltstyp"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Titel"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Type de contenu"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Titre"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -9981,33 +10005,34 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DF2C9DD5-6976-4C54-B07E-54E9E692D4AC}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A8AD2988-7431-4DFD-B87F-7CA4BCD4D5A0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="92de02f7-8a66-43c9-a10c-663538af82ca"/>
+    <ds:schemaRef ds:uri="9211a0c2-e439-43f6-b3c8-c1278e26f744"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A8AD2988-7431-4DFD-B87F-7CA4BCD4D5A0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="9211a0c2-e439-43f6-b3c8-c1278e26f744"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="92de02f7-8a66-43c9-a10c-663538af82ca"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2090E483-B6FB-4E5D-B4FA-7AD1D3C4062C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7F2E194-B260-4C0B-88FC-CB9EA7EAB3B4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -10025,6 +10050,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DF2C9DD5-6976-4C54-B07E-54E9E692D4AC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{42e461c6-591f-4920-9cf0-f1389542f8ad}" enabled="1" method="Standard" siteId="{2cda5d11-f0ac-46b3-967d-af1b2e1bd01a}" removed="0"/>
